--- a/test_full_excel.xlsx
+++ b/test_full_excel.xlsx
@@ -15432,7 +15432,7 @@
     <row r="2">
       <c r="B2" s="322" t="inlineStr">
         <is>
-          <t>XIZMAT KO'RSATISH VA SOTISH REJASI</t>
+          <t>Yotoq mebeli</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
